--- a/data/trans_bre/P1435_2011_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1435_2011_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>464,64%</t>
+          <t>462,55%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,49</t>
+          <t>1,52; 4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,78</t>
+          <t>4,85; 8,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168,25; —</t>
+          <t>149,28; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203,02; 930,77</t>
+          <t>209,13; 1060,72</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>553,36%</t>
+          <t>437,76%</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,62</t>
+          <t>2,98; 5,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,33</t>
+          <t>5,53; 8,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>275,54; 1265,96</t>
+          <t>223,45; 836,95</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27,24</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2957,87%</t>
+          <t>858,14%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,59</t>
+          <t>1,55; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 60,71</t>
+          <t>6,08; 10,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115,43; 2242,14</t>
+          <t>134,43; 2486,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>541,03; 27810,3</t>
+          <t>349,28; 1947,34</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260,65%</t>
+          <t>283,73%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,15</t>
+          <t>1,73; 4,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,18</t>
+          <t>5,27; 9,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182,76; 3080,75</t>
+          <t>189,45; 3251,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103,91; 516,51</t>
+          <t>130,01; 532,49</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,25</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>748,43%</t>
+          <t>430,31%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,92</t>
+          <t>2,6; 3,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 27,07</t>
+          <t>6,39; 8,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>489,49; 2014,94</t>
+          <t>503,14; 2297,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>375,82; 1948,0</t>
+          <t>295,79; 611,38</t>
         </is>
       </c>
     </row>
